--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487544_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487544_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.002</v>
+        <v>8.2272</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8801</v>
+        <v>6.0944</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1219</v>
+        <v>2.1328</v>
       </c>
       <c r="G2" t="n">
         <v>4.4864</v>
@@ -610,13 +610,13 @@
         <v>2.1543</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4119</v>
+        <v>0.6371</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3339</v>
+        <v>0.5481</v>
       </c>
       <c r="U2" t="n">
-        <v>1.078</v>
+        <v>0.089</v>
       </c>
       <c r="V2" t="n">
         <v>4.8664</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8069</v>
+        <v>2.5386</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1454</v>
+        <v>1.69</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6614</v>
+        <v>0.8485</v>
       </c>
       <c r="G3" t="n">
         <v>5.567</v>
@@ -688,13 +688,13 @@
         <v>2.546</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.8384</v>
+        <v>-1.1067</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.891</v>
+        <v>-0.3464</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9474</v>
+        <v>-0.7603</v>
       </c>
       <c r="V3" t="n">
         <v>-0.5507</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. GAYE</t>
+          <t>M. ALVAREZ HERNAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6835</v>
+        <v>1.5319</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2915</v>
+        <v>1.9604</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.608</v>
+        <v>-0.4285</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5566</v>
+        <v>4.4412</v>
       </c>
       <c r="H4" t="n">
-        <v>2.2477</v>
+        <v>-0.1817</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3089</v>
+        <v>4.6229</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1618</v>
+        <v>5.2173</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8789</v>
+        <v>1.4443</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2829</v>
+        <v>3.7731</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.6052</v>
+        <v>-0.7761</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.6311</v>
+        <v>-1.6259</v>
       </c>
       <c r="O4" t="n">
-        <v>0.026</v>
+        <v>0.8498</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-3.5253</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9585</v>
+        <v>-5.8755</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9585</v>
+        <v>2.3502</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.047</v>
+        <v>-0.6006</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0882</v>
+        <v>-0.09</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1352</v>
+        <v>-0.5106000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.8260999999999999</v>
+        <v>1.2166</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.7086</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. ALVAREZ HERNAN</t>
+          <t>M. TRAORE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1488</v>
+        <v>1.4289</v>
       </c>
       <c r="E5" t="n">
-        <v>1.604</v>
+        <v>-1.194</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4552</v>
+        <v>2.6229</v>
       </c>
       <c r="G5" t="n">
-        <v>4.4412</v>
+        <v>1.9821</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1817</v>
+        <v>0.6125</v>
       </c>
       <c r="I5" t="n">
-        <v>4.6229</v>
+        <v>1.3697</v>
       </c>
       <c r="J5" t="n">
-        <v>5.2173</v>
+        <v>2.9009</v>
       </c>
       <c r="K5" t="n">
-        <v>1.4443</v>
+        <v>2.6488</v>
       </c>
       <c r="L5" t="n">
-        <v>3.7731</v>
+        <v>0.2521</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7761</v>
+        <v>-0.9188</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.6259</v>
+        <v>-2.0363</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8498</v>
+        <v>1.1175</v>
       </c>
       <c r="P5" t="n">
-        <v>-3.5253</v>
+        <v>-2.1543</v>
       </c>
       <c r="Q5" t="n">
-        <v>-5.8755</v>
+        <v>-4.8962</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3502</v>
+        <v>2.7419</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9838</v>
+        <v>-0.6143</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4464</v>
+        <v>-0.0823</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5374</v>
+        <v>-0.532</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2166</v>
+        <v>2.2154</v>
       </c>
       <c r="W5" t="n">
-        <v>2.7086</v>
+        <v>0.8837</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.492</v>
+        <v>1.3318</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. TRAORE</t>
+          <t>A. GAYE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.07969999999999999</v>
+        <v>1.3722</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.0621</v>
+        <v>2.0604</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1418</v>
+        <v>-0.6882</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9821</v>
+        <v>2.5566</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6125</v>
+        <v>2.2477</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3697</v>
+        <v>0.3089</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9009</v>
+        <v>4.1618</v>
       </c>
       <c r="K6" t="n">
-        <v>2.6488</v>
+        <v>3.8789</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2521</v>
+        <v>0.2829</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9188</v>
+        <v>-1.6052</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.0363</v>
+        <v>-1.6311</v>
       </c>
       <c r="O6" t="n">
-        <v>1.1175</v>
+        <v>0.026</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.1543</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.8962</v>
+        <v>-1.9585</v>
       </c>
       <c r="R6" t="n">
-        <v>2.7419</v>
+        <v>1.9585</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.9635</v>
+        <v>-0.3583</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9504</v>
+        <v>-0.1429</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.0131</v>
+        <v>-0.2154</v>
       </c>
       <c r="V6" t="n">
-        <v>2.2154</v>
+        <v>-0.8260999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8837</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.3318</v>
+        <v>-0.8260999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0272</v>
+        <v>0.1668</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0784</v>
+        <v>-0.019</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1056</v>
+        <v>0.1858</v>
       </c>
       <c r="G7" t="n">
         <v>-0.0262</v>
@@ -1000,13 +1000,13 @@
         <v>0.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3382</v>
+        <v>-0.1986</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1188</v>
+        <v>-0.0594</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2194</v>
+        <v>-0.1392</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7397</v>
+        <v>-0.5674</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2537</v>
+        <v>-1.1349</v>
       </c>
       <c r="F8" t="n">
-        <v>0.514</v>
+        <v>0.5674</v>
       </c>
       <c r="G8" t="n">
         <v>0.8066</v>
@@ -1078,13 +1078,13 @@
         <v>0.5875</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4507</v>
+        <v>-0.2785</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2376</v>
+        <v>-0.1188</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2131</v>
+        <v>-0.1597</v>
       </c>
       <c r="V8" t="n">
         <v>0.2754</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.6238</v>
+        <v>-2.9396</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3627</v>
+        <v>-0.7587</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.2611</v>
+        <v>-2.1809</v>
       </c>
       <c r="G9" t="n">
         <v>-2.8738</v>
@@ -1156,13 +1156,13 @@
         <v>0.9792</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4539</v>
+        <v>-0.7697000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7722</v>
+        <v>-0.1682</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6817</v>
+        <v>-0.6015</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2754</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.5174</v>
+        <v>-3.8124</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.574</v>
+        <v>-2.0294</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9434</v>
+        <v>-1.783</v>
       </c>
       <c r="G10" t="n">
         <v>1.0486</v>
@@ -1234,13 +1234,13 @@
         <v>0.9792</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4116</v>
+        <v>-0.7066</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8316</v>
+        <v>-0.287</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.58</v>
+        <v>-0.4196</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2166</v>
@@ -1267,19 +1267,19 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>5.8672</v>
+        <v>7.946200000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>4.5901</v>
+        <v>6.669199999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>1.277000000000001</v>
+        <v>1.2768</v>
       </c>
       <c r="G11" t="n">
         <v>17.9885</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3539999999999996</v>
+        <v>0.3540000000000001</v>
       </c>
       <c r="I11" t="n">
         <v>17.6343</v>
@@ -1312,19 +1312,19 @@
         <v>14.6885</v>
       </c>
       <c r="S11" t="n">
-        <v>-6.0752</v>
+        <v>-3.9962</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.8259</v>
+        <v>-0.7468999999999999</v>
       </c>
       <c r="U11" t="n">
         <v>-3.2493</v>
       </c>
       <c r="V11" t="n">
-        <v>5.705</v>
+        <v>5.704999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>9.950700000000001</v>
+        <v>9.950699999999999</v>
       </c>
       <c r="X11" t="n">
         <v>-4.2456</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.3751</v>
+        <v>5.9311</v>
       </c>
       <c r="E12" t="n">
-        <v>3.8133</v>
+        <v>4.5297</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5618</v>
+        <v>1.4014</v>
       </c>
       <c r="G12" t="n">
         <v>2.3252</v>
@@ -1390,13 +1390,13 @@
         <v>2.546</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1246</v>
+        <v>0.4314</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8139999999999999</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6894</v>
+        <v>0.529</v>
       </c>
       <c r="V12" t="n">
         <v>2.5869</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.6297</v>
+        <v>4.4973</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1796</v>
+        <v>3.1007</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4501</v>
+        <v>1.3966</v>
       </c>
       <c r="G13" t="n">
         <v>1.7272</v>
@@ -1468,13 +1468,13 @@
         <v>2.3502</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4097</v>
+        <v>0.4579</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7963</v>
+        <v>0.1247</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3866</v>
+        <v>0.3332</v>
       </c>
       <c r="V13" t="n">
         <v>0.9412</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3185</v>
+        <v>1.7859</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8266</v>
+        <v>1.1336</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4919</v>
+        <v>0.6523</v>
       </c>
       <c r="G14" t="n">
         <v>-0.6767</v>
@@ -1546,13 +1546,13 @@
         <v>2.546</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0007</v>
+        <v>0.4667</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0129</v>
+        <v>0.2941</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0122</v>
+        <v>0.1726</v>
       </c>
       <c r="V14" t="n">
         <v>0.4291</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. DIARRA</t>
+          <t>M. ZORROZUA HERRERO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.023</v>
+        <v>0.3823</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6982</v>
+        <v>1.3632</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6752</v>
+        <v>-0.9809</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.1576</v>
+        <v>-0.0654</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1825</v>
+        <v>0.4856</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.9751</v>
+        <v>-0.551</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9454</v>
+        <v>2.4324</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9049</v>
+        <v>1.7761</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0404</v>
+        <v>0.6563</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.103</v>
+        <v>-2.4978</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0874</v>
+        <v>-1.2905</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.0156</v>
+        <v>-1.2073</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.3709</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.9377</v>
+        <v>-0.9792</v>
       </c>
       <c r="R15" t="n">
-        <v>2.9377</v>
+        <v>2.3502</v>
       </c>
       <c r="S15" t="n">
-        <v>3.5764</v>
+        <v>0.2933</v>
       </c>
       <c r="T15" t="n">
-        <v>3.3565</v>
+        <v>-0.09</v>
       </c>
       <c r="U15" t="n">
-        <v>0.22</v>
+        <v>0.3833</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.3958</v>
+        <v>-1.2166</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.6659</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.73</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. ZORROZUA HERRERO</t>
+          <t>A. MIRANDA GARCIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0538</v>
+        <v>-1.2925</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9538</v>
+        <v>-1.6088</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0076</v>
+        <v>0.3163</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0654</v>
+        <v>-1.5874</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4856</v>
+        <v>-0.6479</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.551</v>
+        <v>-0.9396</v>
       </c>
       <c r="J16" t="n">
-        <v>2.4324</v>
+        <v>-0.5802</v>
       </c>
       <c r="K16" t="n">
-        <v>1.7761</v>
+        <v>-0.5802</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6563</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.4978</v>
+        <v>-1.0073</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2905</v>
+        <v>-0.0677</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.2073</v>
+        <v>-0.9396</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3709</v>
+        <v>0.1958</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3502</v>
+        <v>1.1751</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1427</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4993</v>
+        <v>-0.0494</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3566</v>
+        <v>0.1485</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. PEREZ RUIZ</t>
+          <t>R. QUIROS HERNANDEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9134</v>
+        <v>-1.3805</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5124</v>
+        <v>-2.3385</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.4258</v>
+        <v>0.958</v>
       </c>
       <c r="G17" t="n">
-        <v>-4.1439</v>
+        <v>-4.2436</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9003</v>
+        <v>-3.753</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.2436</v>
+        <v>-0.4905</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.5857</v>
+        <v>-2.5655</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.2212</v>
+        <v>-2.4635</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.3645</v>
+        <v>-0.102</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.5582</v>
+        <v>-1.6781</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6791</v>
+        <v>-1.2895</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.8791</v>
+        <v>-0.3886</v>
       </c>
       <c r="P17" t="n">
-        <v>1.9585</v>
+        <v>2.3502</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9585</v>
+        <v>2.3502</v>
       </c>
       <c r="S17" t="n">
-        <v>1.8804</v>
+        <v>0.5129</v>
       </c>
       <c r="T17" t="n">
-        <v>1.5474</v>
+        <v>0.227</v>
       </c>
       <c r="U17" t="n">
-        <v>0.333</v>
+        <v>0.2858</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6083</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5507</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.159</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. QUIROS HERNANDEZ</t>
+          <t>J. PEREZ RUIZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2828</v>
+        <v>-1.8924</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.1338</v>
+        <v>-0.3063</v>
       </c>
       <c r="F18" t="n">
-        <v>0.851</v>
+        <v>-1.5861</v>
       </c>
       <c r="G18" t="n">
-        <v>-4.2436</v>
+        <v>-4.1439</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.753</v>
+        <v>-0.9003</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4905</v>
+        <v>-3.2436</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.5655</v>
+        <v>-1.5857</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.4635</v>
+        <v>-0.2212</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.102</v>
+        <v>-1.3645</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.6781</v>
+        <v>-2.5582</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2895</v>
+        <v>-0.6791</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3886</v>
+        <v>-1.8791</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3502</v>
+        <v>1.9585</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3502</v>
+        <v>1.9585</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6106</v>
+        <v>0.9013</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4317</v>
+        <v>0.7287</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1789</v>
+        <v>0.1726</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.6083</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.5507</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.159</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. MIRANDA GARCIA</t>
+          <t>D. DIARRA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6529</v>
+        <v>-2.0237</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9158</v>
+        <v>-1.3485</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2629</v>
+        <v>-0.6752</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.5874</v>
+        <v>-2.1576</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6479</v>
+        <v>-0.1825</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9396</v>
+        <v>-1.9751</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5802</v>
+        <v>0.9454</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5802</v>
+        <v>0.9049</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.0404</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0073</v>
+        <v>-3.103</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0677</v>
+        <v>-1.0874</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9396</v>
+        <v>-2.0156</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1958</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9792</v>
+        <v>-2.9377</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1751</v>
+        <v>2.9377</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2614</v>
+        <v>1.5297</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3564</v>
+        <v>1.3098</v>
       </c>
       <c r="U19" t="n">
-        <v>0.095</v>
+        <v>0.22</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.3958</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.6659</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3606</v>
+        <v>-2.8234</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3234</v>
+        <v>-0.7328</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.0372</v>
+        <v>-2.0907</v>
       </c>
       <c r="G20" t="n">
         <v>-3.4519</v>
@@ -2014,13 +2014,13 @@
         <v>1.3709</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6995</v>
+        <v>0.2367</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6693</v>
+        <v>0.26</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0302</v>
+        <v>-0.0232</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.7668</v>
+        <v>-3.6331</v>
       </c>
       <c r="E21" t="n">
         <v>-2.5757</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1911</v>
+        <v>-1.0574</v>
       </c>
       <c r="G21" t="n">
         <v>-3.5011</v>
@@ -2092,13 +2092,13 @@
         <v>3.5253</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0762</v>
+        <v>0.2098</v>
       </c>
       <c r="T21" t="n">
         <v>0.0159</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0603</v>
+        <v>0.1939</v>
       </c>
       <c r="V21" t="n">
         <v>-2.8878</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.1832</v>
+        <v>-5.4179</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.3122</v>
+        <v>-2.4935</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.8709</v>
+        <v>-2.9244</v>
       </c>
       <c r="G22" t="n">
         <v>-2.2133</v>
@@ -2170,13 +2170,13 @@
         <v>3.3294</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1714</v>
+        <v>0.9366</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2923</v>
+        <v>0.5264</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4637</v>
+        <v>0.4102</v>
       </c>
       <c r="V22" t="n">
         <v>-3.5537</v>
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.8672</v>
+        <v>-5.8669</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.277</v>
+        <v>-1.2769</v>
       </c>
       <c r="F23" t="n">
         <v>-4.5901</v>
@@ -2257,13 +2257,13 @@
         <v>2.8259</v>
       </c>
       <c r="V23" t="n">
-        <v>-5.705</v>
+        <v>-5.704999999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>4.245599999999999</v>
+        <v>4.2456</v>
       </c>
       <c r="X23" t="n">
-        <v>-9.950800000000001</v>
+        <v>-9.950799999999999</v>
       </c>
     </row>
   </sheetData>
